--- a/results/pooled_results_OR_multi_exposure_models_personality_excludes_rheumatism.xlsx
+++ b/results/pooled_results_OR_multi_exposure_models_personality_excludes_rheumatism.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\Old\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F160996C-6535-4CD8-B3D4-E6DA613B2BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EB1D28-B3B4-4827-838C-9EB5D9E664BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{797B858C-DA94-466A-A931-46BE830858D9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="16752" xr2:uid="{797B858C-DA94-466A-A931-46BE830858D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>Depression</t>
   </si>
@@ -153,6 +153,9 @@
   <si>
     <t>Excludes those with rheumatism</t>
   </si>
+  <si>
+    <t>Depression + Hostility + Authority</t>
+  </si>
 </sst>
 </file>
 
@@ -160,7 +163,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -262,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -278,8 +281,9 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -292,7 +296,9 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,6 +642,7 @@
     <col min="7" max="7" width="8.88671875" style="2"/>
     <col min="8" max="8" width="2.77734375" customWidth="1"/>
     <col min="13" max="13" width="2.77734375" customWidth="1"/>
+    <col min="18" max="18" width="2.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.3">
@@ -680,24 +687,30 @@
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="I5" s="14" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="I5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="16"/>
-      <c r="N5" s="14" t="s">
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+      <c r="N5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
+      <c r="S5" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="17"/>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="D6" s="7"/>
@@ -748,6 +761,19 @@
       <c r="Q7" s="9" t="s">
         <v>15</v>
       </c>
+      <c r="R7" s="4"/>
+      <c r="S7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
@@ -759,23 +785,27 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="11"/>
       <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="13"/>
+      <c r="K8" s="14"/>
       <c r="L8" s="11"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="11"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="11"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C9" s="6">
@@ -804,6 +834,18 @@
       </c>
       <c r="L9" s="11">
         <v>0.94417399999999996</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.9989711</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.57271309999999997</v>
+      </c>
+      <c r="U9" s="1">
+        <v>1.7424839999999999</v>
+      </c>
+      <c r="V9" s="11">
+        <v>0.99709999999999999</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -834,6 +876,18 @@
       <c r="L10" s="11">
         <v>0.31135200000000002</v>
       </c>
+      <c r="S10" s="1">
+        <v>1.3363836</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0.72629909999999998</v>
+      </c>
+      <c r="U10" s="1">
+        <v>2.4589340000000002</v>
+      </c>
+      <c r="V10" s="11">
+        <v>0.35110000000000002</v>
+      </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C11" s="6">
@@ -863,6 +917,18 @@
       </c>
       <c r="L11" s="12">
         <v>1.2968E-2</v>
+      </c>
+      <c r="S11" s="10">
+        <v>2.2658122000000001</v>
+      </c>
+      <c r="T11" s="10">
+        <v>1.0785597</v>
+      </c>
+      <c r="U11" s="10">
+        <v>4.7599640000000001</v>
+      </c>
+      <c r="V11" s="12">
+        <v>3.082E-2</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
@@ -883,10 +949,10 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="13"/>
+      <c r="F13" s="14"/>
       <c r="G13" s="11"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -895,10 +961,13 @@
       <c r="N13" s="1">
         <v>1</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="O13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="14"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C14" s="6">
@@ -927,6 +996,18 @@
       </c>
       <c r="Q14" s="11">
         <v>0.41199799999999998</v>
+      </c>
+      <c r="S14" s="1">
+        <v>1.2176022</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.73647560000000001</v>
+      </c>
+      <c r="U14" s="1">
+        <v>2.0130400000000002</v>
+      </c>
+      <c r="V14" s="11">
+        <v>0.44252999999999998</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
@@ -956,6 +1037,18 @@
       </c>
       <c r="Q15" s="12">
         <v>4.1428E-2</v>
+      </c>
+      <c r="S15" s="19">
+        <v>1.6777521</v>
+      </c>
+      <c r="T15" s="19">
+        <v>0.92021609999999998</v>
+      </c>
+      <c r="U15" s="19">
+        <v>3.0589029999999999</v>
+      </c>
+      <c r="V15" s="20">
+        <v>9.1230000000000006E-2</v>
       </c>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.3">
@@ -965,8 +1058,12 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="11"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="11"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>18</v>
       </c>
@@ -977,20 +1074,24 @@
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="13"/>
+      <c r="K17" s="14"/>
       <c r="N17" s="1">
         <v>1</v>
       </c>
-      <c r="O17" s="13" t="s">
+      <c r="O17" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P17" s="13"/>
+      <c r="P17" s="14"/>
       <c r="Q17" s="11"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S17" s="1"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="11"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C18" s="6">
         <v>1</v>
       </c>
@@ -1019,8 +1120,20 @@
       <c r="Q18" s="11">
         <v>0.165635</v>
       </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S18" s="1">
+        <v>1.5099815999999999</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0.80497529999999995</v>
+      </c>
+      <c r="U18" s="1">
+        <v>2.8324400000000001</v>
+      </c>
+      <c r="V18" s="11">
+        <v>0.19897999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C19" s="6">
         <v>2</v>
       </c>
@@ -1049,8 +1162,20 @@
       <c r="Q19" s="11">
         <v>6.9016999999999995E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S19" s="1">
+        <v>1.7153153999999999</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0.8434564</v>
+      </c>
+      <c r="U19" s="1">
+        <v>3.4883929999999999</v>
+      </c>
+      <c r="V19" s="11">
+        <v>0.13617000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C20" s="6">
         <v>3</v>
       </c>
@@ -1079,12 +1204,24 @@
       <c r="Q20" s="12">
         <v>4.6933000000000002E-2</v>
       </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S20" s="19">
+        <v>2.2664122</v>
+      </c>
+      <c r="T20" s="19">
+        <v>0.79199529999999996</v>
+      </c>
+      <c r="U20" s="19">
+        <v>6.4856749999999996</v>
+      </c>
+      <c r="V20" s="20">
+        <v>0.12701999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C21" s="6"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>23</v>
       </c>
@@ -1126,8 +1263,21 @@
       <c r="Q22" s="12">
         <v>9.7900000000000005E-4</v>
       </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R22" s="3"/>
+      <c r="S22" s="10">
+        <v>0.96049039999999997</v>
+      </c>
+      <c r="T22" s="10">
+        <v>0.93704069999999995</v>
+      </c>
+      <c r="U22" s="10">
+        <v>0.98452700000000004</v>
+      </c>
+      <c r="V22" s="12">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="G23" s="11"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1137,8 +1287,12 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="11"/>
-    </row>
-    <row r="24" spans="2:17" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="11"/>
+    </row>
+    <row r="24" spans="2:22" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
@@ -1178,8 +1332,20 @@
       <c r="Q24" s="11">
         <v>0.105602</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S24" s="1">
+        <v>0.94424909999999995</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0.88597440000000005</v>
+      </c>
+      <c r="U24" s="1">
+        <v>1.0063569999999999</v>
+      </c>
+      <c r="V24" s="11">
+        <v>7.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="G25" s="11"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1189,8 +1355,12 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="11"/>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="11"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>6</v>
       </c>
@@ -1200,29 +1370,33 @@
       <c r="D26" s="1">
         <v>1</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="13"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="11"/>
       <c r="I26" s="1">
         <v>1</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K26" s="13"/>
+      <c r="K26" s="14"/>
       <c r="L26" s="11"/>
       <c r="N26" s="1">
         <v>1</v>
       </c>
-      <c r="O26" s="13" t="s">
+      <c r="O26" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P26" s="13"/>
+      <c r="P26" s="14"/>
       <c r="Q26" s="11"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S26" s="1"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="11"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C27" s="3" t="s">
         <v>1</v>
       </c>
@@ -1262,8 +1436,20 @@
       <c r="Q27" s="11">
         <v>0.53977799999999998</v>
       </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S27" s="1">
+        <v>1.2623089999999999</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0.67635109999999998</v>
+      </c>
+      <c r="U27" s="1">
+        <v>2.3559130000000001</v>
+      </c>
+      <c r="V27" s="11">
+        <v>0.4642</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C28" s="3" t="s">
         <v>2</v>
       </c>
@@ -1303,8 +1489,20 @@
       <c r="Q28" s="11">
         <v>0.21263899999999999</v>
       </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S28" s="1">
+        <v>1.6672020000000001</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0.83554070000000003</v>
+      </c>
+      <c r="U28" s="1">
+        <v>3.3266640000000001</v>
+      </c>
+      <c r="V28" s="11">
+        <v>0.14692</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="G29" s="11"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1314,8 +1512,12 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="11"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="11"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>7</v>
       </c>
@@ -1325,29 +1527,33 @@
       <c r="D30" s="1">
         <v>1</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="13"/>
+      <c r="F30" s="14"/>
       <c r="G30" s="11"/>
       <c r="I30" s="1">
         <v>1</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K30" s="13"/>
+      <c r="K30" s="14"/>
       <c r="L30" s="11"/>
       <c r="N30" s="1">
         <v>1</v>
       </c>
-      <c r="O30" s="13" t="s">
+      <c r="O30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P30" s="13"/>
+      <c r="P30" s="14"/>
       <c r="Q30" s="11"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S30" s="1"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="11"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C31" s="3" t="s">
         <v>4</v>
       </c>
@@ -1387,8 +1593,20 @@
       <c r="Q31" s="11">
         <v>0.136631</v>
       </c>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S31" s="1">
+        <v>0.69088329999999998</v>
+      </c>
+      <c r="T31" s="1">
+        <v>0.4399729</v>
+      </c>
+      <c r="U31" s="1">
+        <v>1.084884</v>
+      </c>
+      <c r="V31" s="11">
+        <v>0.1082</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="G32" s="11"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -1398,8 +1616,12 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="11"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="11"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>8</v>
       </c>
@@ -1409,29 +1631,33 @@
       <c r="D33" s="1">
         <v>1</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="13"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="11"/>
       <c r="I33" s="1">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K33" s="13"/>
+      <c r="K33" s="14"/>
       <c r="L33" s="11"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
-      <c r="O33" s="13" t="s">
+      <c r="O33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P33" s="13"/>
+      <c r="P33" s="14"/>
       <c r="Q33" s="11"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S33" s="1"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="11"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C34" s="3" t="s">
         <v>10</v>
       </c>
@@ -1471,8 +1697,20 @@
       <c r="Q34" s="11">
         <v>0.70957599999999998</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S34" s="1">
+        <v>1.2620281</v>
+      </c>
+      <c r="T34" s="1">
+        <v>0.4954789</v>
+      </c>
+      <c r="U34" s="1">
+        <v>3.214496</v>
+      </c>
+      <c r="V34" s="11">
+        <v>0.62548999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C35" s="3" t="s">
         <v>11</v>
       </c>
@@ -1512,8 +1750,20 @@
       <c r="Q35" s="11">
         <v>0.64464200000000005</v>
       </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S35" s="1">
+        <v>1.3251195</v>
+      </c>
+      <c r="T35" s="1">
+        <v>0.40599350000000001</v>
+      </c>
+      <c r="U35" s="1">
+        <v>4.3250489999999999</v>
+      </c>
+      <c r="V35" s="11">
+        <v>0.64076</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="G36" s="11"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -1523,8 +1773,12 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="11"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="11"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>25</v>
       </c>
@@ -1534,29 +1788,33 @@
       <c r="D37" s="1">
         <v>1</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="13"/>
+      <c r="F37" s="14"/>
       <c r="G37" s="11"/>
       <c r="I37" s="1">
         <v>1</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K37" s="13"/>
+      <c r="K37" s="14"/>
       <c r="L37" s="11"/>
       <c r="N37" s="1">
         <v>1</v>
       </c>
-      <c r="O37" s="13" t="s">
+      <c r="O37" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P37" s="13"/>
+      <c r="P37" s="14"/>
       <c r="Q37" s="11"/>
-    </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S37" s="1"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="11"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C38" s="3" t="s">
         <v>27</v>
       </c>
@@ -1598,8 +1856,21 @@
       <c r="Q38" s="12">
         <v>5.1869999999999998E-3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R38" s="3"/>
+      <c r="S38" s="10">
+        <v>2.3499355</v>
+      </c>
+      <c r="T38" s="10">
+        <v>1.2870102999999999</v>
+      </c>
+      <c r="U38" s="10">
+        <v>4.2907169999999999</v>
+      </c>
+      <c r="V38" s="12">
+        <v>5.4400000000000004E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="G39" s="11"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -1609,8 +1880,12 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="11"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="11"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>28</v>
       </c>
@@ -1620,29 +1895,33 @@
       <c r="D40" s="1">
         <v>1</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="13"/>
+      <c r="F40" s="14"/>
       <c r="G40" s="11"/>
       <c r="I40" s="1">
         <v>1</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K40" s="13"/>
+      <c r="K40" s="14"/>
       <c r="L40" s="11"/>
       <c r="N40" s="1">
         <v>1</v>
       </c>
-      <c r="O40" s="13" t="s">
+      <c r="O40" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="P40" s="13"/>
+      <c r="P40" s="14"/>
       <c r="Q40" s="11"/>
-    </row>
-    <row r="41" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S40" s="1"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="11"/>
+    </row>
+    <row r="41" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
         <v>4</v>
@@ -1656,7 +1935,7 @@
       <c r="F41" s="8">
         <v>4.2824084999999998</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="13">
         <v>4.0969999999999999E-2</v>
       </c>
       <c r="H41" s="4"/>
@@ -1669,7 +1948,7 @@
       <c r="K41" s="8">
         <v>4.1929610999999998</v>
       </c>
-      <c r="L41" s="17">
+      <c r="L41" s="13">
         <v>4.8481999999999997E-2</v>
       </c>
       <c r="M41" s="4"/>
@@ -1682,13 +1961,35 @@
       <c r="P41" s="8">
         <v>4.3429754999999997</v>
       </c>
-      <c r="Q41" s="17">
+      <c r="Q41" s="13">
         <v>3.7714999999999999E-2</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="8">
+        <v>2.0789504999999999</v>
+      </c>
+      <c r="T41" s="8">
+        <v>1.0170315000000001</v>
+      </c>
+      <c r="U41" s="8">
+        <v>4.249657</v>
+      </c>
+      <c r="V41" s="13">
+        <v>4.4839999999999998E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="O37:P37"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="O33:P33"/>
@@ -1705,14 +2006,6 @@
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="O40:P40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
